--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261014.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261014.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,360,000</t>
+          <t>3,521,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,521,000</t>
+          <t>2,360,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
